--- a/eval/gold_scenarios/q3_pass_dc2_02.xlsx
+++ b/eval/gold_scenarios/q3_pass_dc2_02.xlsx
@@ -759,12 +759,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>&lt;attribute_A_description&gt;</t>
+          <t>Current-period accrual data is loaded completely and accurately.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>&lt;attribute_A_toc_procedure&gt;</t>
+          <t>Agree current-period load totals to the upstream data feed.</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>&lt;attribute_B_description&gt;</t>
+          <t>Variances above threshold have a recorded explanation.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>&lt;attribute_B_toc_procedure&gt;</t>
+          <t>For each variance above threshold, inspect the explanation column.</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>&lt;attribute_C_description&gt;</t>
+          <t>Explanations are consistent with upstream source data.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>&lt;attribute_C_toc_procedure&gt;</t>
+          <t>For each explanation, agree the referenced figure to the upstream source.</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>&lt;attribute_D_description&gt;</t>
+          <t>Reviewer signed off on the completed variance-analysis spreadsheet.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>&lt;attribute_D_toc_procedure&gt;</t>
+          <t>Inspect the reviewer sign-off line on the variance-analysis workbook.</t>
         </is>
       </c>
     </row>
